--- a/core/report_templates/uvnk_8p_report_template.xlsx
+++ b/core/report_templates/uvnk_8p_report_template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="104">
   <si>
     <t>Звіт по проведеним роботам в установці УВНК-8П</t>
   </si>
@@ -22,9 +22,6 @@
   </si>
   <si>
     <t>Плавильник (ПІБ)</t>
-  </si>
-  <si>
-    <t>ОТК (ПІБ)</t>
   </si>
   <si>
     <t>Номер цехової плавки</t>
@@ -709,11 +706,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1416958374"/>
-        <c:axId val="576066927"/>
+        <c:axId val="1129175756"/>
+        <c:axId val="755968127"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1416958374"/>
+        <c:axId val="1129175756"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -777,10 +774,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576066927"/>
+        <c:crossAx val="755968127"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="576066927"/>
+        <c:axId val="755968127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -857,7 +854,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1416958374"/>
+        <c:crossAx val="1129175756"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -983,11 +980,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="609207743"/>
-        <c:axId val="1487224203"/>
+        <c:axId val="1602906582"/>
+        <c:axId val="1687980100"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="609207743"/>
+        <c:axId val="1602906582"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1043,10 +1040,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1487224203"/>
+        <c:crossAx val="1687980100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1487224203"/>
+        <c:axId val="1687980100"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1123,7 +1120,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="609207743"/>
+        <c:crossAx val="1602906582"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1350,11 +1347,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1885024105"/>
-        <c:axId val="1543638437"/>
+        <c:axId val="713313963"/>
+        <c:axId val="1715015547"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1885024105"/>
+        <c:axId val="713313963"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1410,10 +1407,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1543638437"/>
+        <c:crossAx val="1715015547"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1543638437"/>
+        <c:axId val="1715015547"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1490,7 +1487,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1885024105"/>
+        <c:crossAx val="713313963"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1582,11 +1579,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="981636300"/>
-        <c:axId val="1339804502"/>
+        <c:axId val="500147722"/>
+        <c:axId val="1815762845"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="981636300"/>
+        <c:axId val="500147722"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1642,10 +1639,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1339804502"/>
+        <c:crossAx val="1815762845"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1339804502"/>
+        <c:axId val="1815762845"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1722,7 +1719,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="981636300"/>
+        <c:crossAx val="500147722"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1816,11 +1813,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="822547455"/>
-        <c:axId val="50259249"/>
+        <c:axId val="148489387"/>
+        <c:axId val="458306226"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="822547455"/>
+        <c:axId val="148489387"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1876,10 +1873,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50259249"/>
+        <c:crossAx val="458306226"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50259249"/>
+        <c:axId val="458306226"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1964,7 +1961,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="822547455"/>
+        <c:crossAx val="148489387"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2058,11 +2055,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="441996783"/>
-        <c:axId val="62035900"/>
+        <c:axId val="2095912013"/>
+        <c:axId val="153278979"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="441996783"/>
+        <c:axId val="2095912013"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2118,10 +2115,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62035900"/>
+        <c:crossAx val="153278979"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62035900"/>
+        <c:axId val="153278979"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2206,7 +2203,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="441996783"/>
+        <c:crossAx val="2095912013"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2638,31 +2635,31 @@
       <c r="B5" s="6"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="7"/>
+      <c r="B7" s="6"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="6"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="9"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
@@ -2674,17 +2671,17 @@
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="9"/>
+      <c r="B12" s="10"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11"/>
+      <c r="B13" s="7"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="10"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="7"/>
+      <c r="B14" s="6"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
@@ -2699,168 +2696,171 @@
       <c r="B16" s="6"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="11"/>
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11"/>
-      <c r="B18" s="7"/>
+      <c r="B18" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="B19" s="7"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="7"/>
+      <c r="B20" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="B22" s="7"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="7"/>
+      <c r="B23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="13" t="s">
+      <c r="A24" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="s">
-        <v>14</v>
-      </c>
+      <c r="A25" s="15"/>
       <c r="B25" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15"/>
       <c r="B26" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15"/>
       <c r="B27" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15"/>
       <c r="B28" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15"/>
       <c r="B29" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15"/>
       <c r="B30" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15"/>
       <c r="B31" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15"/>
       <c r="B32" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15"/>
       <c r="B33" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15"/>
       <c r="B34" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15"/>
       <c r="B35" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15"/>
       <c r="B36" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>45</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -2869,16 +2869,16 @@
         <v>47</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15"/>
       <c r="B38" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="39">
@@ -2887,26 +2887,20 @@
         <v>50</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15"/>
+      <c r="A40" s="16"/>
       <c r="B40" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16"/>
-      <c r="B41" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>52</v>
-      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="4"/>
     </row>
     <row r="45">
       <c r="B45" s="4"/>
@@ -5772,15 +5766,12 @@
     </row>
     <row r="999">
       <c r="B999" s="4"/>
-    </row>
-    <row r="1000">
-      <c r="B1000" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A25:A41"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A24:A40"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5805,7 +5796,7 @@
   <sheetData>
     <row r="1" ht="57.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5825,12 +5816,12 @@
     </row>
     <row r="4">
       <c r="A4" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
       <c r="E4" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -5839,35 +5830,35 @@
     </row>
     <row r="5">
       <c r="A5" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" s="22">
         <v>0.0</v>
@@ -5907,11 +5898,11 @@
     </row>
     <row r="8">
       <c r="A8" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" s="22">
         <v>2.0</v>
@@ -5931,11 +5922,11 @@
     </row>
     <row r="9">
       <c r="A9" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" s="22">
         <v>3.0</v>
@@ -5972,11 +5963,11 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="22">
         <v>5.0</v>
@@ -5996,11 +5987,11 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" s="22">
         <v>6.0</v>
@@ -6040,11 +6031,11 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" s="22">
         <v>8.0</v>
@@ -6084,11 +6075,11 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" s="22">
         <v>10.0</v>
@@ -6108,11 +6099,11 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" s="22">
         <v>11.0</v>
@@ -6132,11 +6123,11 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" s="22">
         <v>12.0</v>
@@ -6176,11 +6167,11 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="22">
         <v>14.0</v>
@@ -6220,11 +6211,11 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E22" s="22">
         <v>16.0</v>
@@ -6244,11 +6235,11 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" s="22">
         <v>17.0</v>
@@ -6557,7 +6548,7 @@
   <sheetData>
     <row r="1" ht="57.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6585,18 +6576,18 @@
     </row>
     <row r="4">
       <c r="A4" s="29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
       <c r="E4" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
       <c r="J4" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -6606,50 +6597,50 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="J5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" s="22">
         <v>0.0</v>
@@ -6684,11 +6675,11 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" s="22">
         <v>1.0</v>
@@ -6756,11 +6747,11 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" s="22">
         <v>3.0</v>
@@ -6861,11 +6852,11 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E12" s="22">
         <v>6.0</v>
@@ -6900,7 +6891,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="33"/>
       <c r="C13" s="34"/>
@@ -6937,11 +6928,11 @@
     </row>
     <row r="14">
       <c r="A14" s="35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" s="22">
         <v>8.0</v>
@@ -6976,11 +6967,11 @@
     </row>
     <row r="15">
       <c r="A15" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="22">
         <v>9.0</v>
@@ -7015,11 +7006,11 @@
     </row>
     <row r="16">
       <c r="A16" s="35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" s="22">
         <v>10.0</v>
@@ -7054,11 +7045,11 @@
     </row>
     <row r="17">
       <c r="A17" s="35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" s="22">
         <v>11.0</v>
@@ -7093,11 +7084,11 @@
     </row>
     <row r="18">
       <c r="A18" s="35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" s="22">
         <v>12.0</v>
@@ -7546,7 +7537,7 @@
         <v>0.0</v>
       </c>
       <c r="P31" s="36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32">
